--- a/src/assets/img/data.xlsx
+++ b/src/assets/img/data.xlsx
@@ -1,26 +1,171 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\220 - Centre Européen de Formation\99 - Refonte\Trouve-ton-artisan\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FBBF063-8F40-4749-A284-ADAEF3AA35EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{3B42AFDC-023C-4E63-AA25-CBA0BBA52FF3}"/>
+    <workbookView windowWidth="23115" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="data2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Spécialité</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Ville</t>
+  </si>
+  <si>
+    <t>A propos</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Site Web</t>
+  </si>
+  <si>
+    <t>Catégorie</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>Boucherie Dumont</t>
+  </si>
+  <si>
+    <t>Boucher</t>
+  </si>
+  <si>
+    <t>Lyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lorem ipsum dolor sit amet, consectetur adipiscing elit. Phasellus eleifend ante sem, id volutpat massa fermentum nec. Praesent volutpat scelerisque mauris, quis sollicitudin tellus sollicitudin. </t>
+  </si>
+  <si>
+    <t>boucherie.dumond@gmail.com</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
+  </si>
+  <si>
+    <t>Au pain chaud</t>
+  </si>
+  <si>
+    <t>Boulanger</t>
+  </si>
+  <si>
+    <t>Montélimar</t>
+  </si>
+  <si>
+    <t>aupainchaud@hotmail.com</t>
+  </si>
+  <si>
+    <t>Chocolaterie Labbé</t>
+  </si>
+  <si>
+    <t>Chocolatier</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>chocolaterie-labbe@gmail.com</t>
+  </si>
+  <si>
+    <t>https://chocolaterie-labbe.fr</t>
+  </si>
+  <si>
+    <t>Traiteur Truchon</t>
+  </si>
+  <si>
+    <t>Traiteur</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>contact@truchon-traiteur.fr</t>
+  </si>
+  <si>
+    <t>https://truchon-traiteur.fr</t>
+  </si>
+  <si>
+    <t>Orville Salmons</t>
+  </si>
+  <si>
+    <t>Chauffagiste</t>
+  </si>
+  <si>
+    <t>Evian</t>
+  </si>
+  <si>
+    <t>o-salmons@live.com</t>
+  </si>
+  <si>
+    <t>Bâtiment</t>
+  </si>
+  <si>
+    <t>Mont Blanc Eléctricité</t>
+  </si>
+  <si>
+    <t>Electricien</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>Chamonix</t>
+  </si>
+  <si>
+    <t>contact@mont-blanc-electricite.com</t>
+  </si>
+  <si>
+    <t>https://mont-blanc-electricite.com</t>
+  </si>
+  <si>
+    <t>Boutot &amp; fils</t>
+  </si>
+  <si>
+    <t>Menuisier</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>Bourg-en-bresse</t>
+  </si>
+  <si>
+    <t>boutot-menuiserie@gmail.com</t>
+  </si>
+  <si>
+    <t>https://boutot-menuiserie.com</t>
+  </si>
   <si>
     <t>Vallis Bellemare</t>
   </si>
@@ -31,16 +176,28 @@
     <t>Vienne</t>
   </si>
   <si>
-    <t xml:space="preserve">Lorem ipsum dolor sit amet, consectetur adipiscing elit. Phasellus eleifend ante sem, id volutpat massa fermentum nec. Praesent volutpat scelerisque mauris, quis sollicitudin tellus sollicitudin. </t>
-  </si>
-  <si>
     <t>v.bellemare@gmail.com</t>
   </si>
   <si>
     <t>https://plomberie-bellemare.com</t>
   </si>
   <si>
-    <t>Bâtiment</t>
+    <t>Claude Quinn</t>
+  </si>
+  <si>
+    <t>Bijoutier</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Aix-les-bains</t>
+  </si>
+  <si>
+    <t>claude.quinn@gmail.com</t>
+  </si>
+  <si>
+    <t>Fabrication</t>
   </si>
   <si>
     <t>Amitee Lécuyer</t>
@@ -49,9 +206,6 @@
     <t>Couturier</t>
   </si>
   <si>
-    <t>4.5</t>
-  </si>
-  <si>
     <t>Annecy</t>
   </si>
   <si>
@@ -61,18 +215,39 @@
     <t>https://lecuyer-couture.com</t>
   </si>
   <si>
-    <t>Fabrication</t>
+    <t>Ernest Carignan</t>
+  </si>
+  <si>
+    <t>Ferronier</t>
+  </si>
+  <si>
+    <t>Le Puy-en-Velay</t>
+  </si>
+  <si>
+    <t>e-carigan@hotmail.com</t>
+  </si>
+  <si>
+    <t>Royden Charbonneau</t>
+  </si>
+  <si>
+    <t>Coiffeur</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>Saint-Priest</t>
+  </si>
+  <si>
+    <t>r.charbonneau@gmail.com</t>
+  </si>
+  <si>
+    <t>Services</t>
   </si>
   <si>
     <t>Leala Dennis</t>
   </si>
   <si>
-    <t>Coiffeur</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
     <t>Chambéry</t>
   </si>
   <si>
@@ -82,40 +257,34 @@
     <t>https://coiffure-leala-chambery.fr</t>
   </si>
   <si>
-    <t>Services</t>
-  </si>
-  <si>
-    <t>Chocolaterie Labbé</t>
-  </si>
-  <si>
-    <t>Chocolatier</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>chocolaterie-labbe@gmail.com</t>
-  </si>
-  <si>
-    <t>https://chocolaterie-labbe.fr</t>
-  </si>
-  <si>
-    <t>Alimentation</t>
-  </si>
-  <si>
-    <t>Claude Quinn</t>
-  </si>
-  <si>
-    <t>Bijoutier</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>Aix-les-bains</t>
-  </si>
-  <si>
-    <t>claude.quinn@gmail.com</t>
+    <t>C'est sup'hair</t>
+  </si>
+  <si>
+    <t>Romans-sur-Isère</t>
+  </si>
+  <si>
+    <t>sup-hair@gmail.com</t>
+  </si>
+  <si>
+    <t>https://sup-hair.fr</t>
+  </si>
+  <si>
+    <t>Le monde des fleurs</t>
+  </si>
+  <si>
+    <t>Fleuriste</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>Annonay</t>
+  </si>
+  <si>
+    <t>contact@le-monde-des-fleurs-annonay.fr</t>
+  </si>
+  <si>
+    <t>https://le-monde-des-fleurs-annonay.fr</t>
   </si>
   <si>
     <t>Valérie Laderoute</t>
@@ -130,24 +299,6 @@
     <t>v-laredoute@gmail.com</t>
   </si>
   <si>
-    <t>Boutot &amp; fils</t>
-  </si>
-  <si>
-    <t>Menuisier</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>Bourg-en-bresse</t>
-  </si>
-  <si>
-    <t>boutot-menuiserie@gmail.com</t>
-  </si>
-  <si>
-    <t>https://boutot-menuiserie.com</t>
-  </si>
-  <si>
     <t>CM Graphisme</t>
   </si>
   <si>
@@ -161,190 +312,78 @@
   </si>
   <si>
     <t>https://cm-graphisme.com</t>
-  </si>
-  <si>
-    <t>Orville Salmons</t>
-  </si>
-  <si>
-    <t>Chauffagiste</t>
-  </si>
-  <si>
-    <t>Evian</t>
-  </si>
-  <si>
-    <t>o-salmons@live.com</t>
-  </si>
-  <si>
-    <t>Au pain chaud</t>
-  </si>
-  <si>
-    <t>Boulanger</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>Montélimar</t>
-  </si>
-  <si>
-    <t>aupainchaud@hotmail.com</t>
-  </si>
-  <si>
-    <t>Boucherie Dumont</t>
-  </si>
-  <si>
-    <t>Boucher</t>
-  </si>
-  <si>
-    <t>Lyon</t>
-  </si>
-  <si>
-    <t>boucherie.dumond@gmail.com</t>
-  </si>
-  <si>
-    <t>Mont Blanc Eléctricité</t>
-  </si>
-  <si>
-    <t>Electricien</t>
-  </si>
-  <si>
-    <t>Chamonix</t>
-  </si>
-  <si>
-    <t>contact@mont-blanc-electricite.com</t>
-  </si>
-  <si>
-    <t>https://mont-blanc-electricite.com</t>
-  </si>
-  <si>
-    <t>Traiteur Truchon</t>
-  </si>
-  <si>
-    <t>Traiteur</t>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>contact@truchon-traiteur.fr</t>
-  </si>
-  <si>
-    <t>https://truchon-traiteur.fr</t>
-  </si>
-  <si>
-    <t>Le monde des fleurs</t>
-  </si>
-  <si>
-    <t>Fleuriste</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>Annonay</t>
-  </si>
-  <si>
-    <t>contact@le-monde-des-fleurs-annonay.fr</t>
-  </si>
-  <si>
-    <t>https://le-monde-des-fleurs-annonay.fr</t>
-  </si>
-  <si>
-    <t>Royden Charbonneau</t>
-  </si>
-  <si>
-    <t>Saint-Priest</t>
-  </si>
-  <si>
-    <t>r.charbonneau@gmail.com</t>
-  </si>
-  <si>
-    <t>Ernest Carignan</t>
-  </si>
-  <si>
-    <t>Ferronier</t>
-  </si>
-  <si>
-    <t>Le Puy-en-Velay</t>
-  </si>
-  <si>
-    <t>e-carigan@hotmail.com</t>
-  </si>
-  <si>
-    <t>C'est sup'hair</t>
-  </si>
-  <si>
-    <t>Romans-sur-Isère</t>
-  </si>
-  <si>
-    <t>sup-hair@gmail.com</t>
-  </si>
-  <si>
-    <t>https://sup-hair.fr</t>
-  </si>
-  <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>Spécialité</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>A propos</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Site Web</t>
-  </si>
-  <si>
-    <t>Catégorie</t>
-  </si>
-  <si>
-    <t>Top</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Aptos Display"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,7 +391,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -360,35 +399,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -396,7 +414,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -404,14 +422,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -419,22 +430,14 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -442,14 +445,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -462,175 +486,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -640,6 +677,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -665,7 +717,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -700,15 +752,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -724,17 +767,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,108 +787,133 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20 % - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40 % - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60 % - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Avertissement" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Calcul" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Cellule liée" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Entrée" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Insatisfaisant" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Neutre" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Satisfaisant" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Sortie" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texte explicatif" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Titre" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Titre 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Titre 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Titre 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Titre 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -900,7 +962,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -933,26 +995,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -985,23 +1030,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1163,537 +1191,538 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1039988A-4603-464C-9601-E569556012AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.5703125" customWidth="1"/>
-    <col min="6" max="6" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8.85833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="23.125" customWidth="1"/>
+    <col min="6" max="6" width="17.25" customWidth="1"/>
+    <col min="7" max="7" width="36.2833333333333" customWidth="1"/>
+    <col min="8" max="8" width="12.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="9.85833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4.5</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>16</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4.8</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" t="s">
         <v>71</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" t="s">
-        <v>20</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I18">
+  <sortState ref="A2:I18">
     <sortCondition ref="H2:H18"/>
     <sortCondition ref="B2:B18"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" display="boucherie.dumond@gmail.com"/>
+    <hyperlink ref="F3" r:id="rId2" display="aupainchaud@hotmail.com"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://chocolaterie-labbe.fr"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>